--- a/test.xlsx
+++ b/test.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUU 002 0717" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUU 002 0805" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUU 003 0717" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUU 003 0805" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,20 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00276A3C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -124,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -146,6 +161,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4316,6 +4343,2764 @@
         <is>
           <t>If Coverage Type = Employers Liability (All States) OR Employers Liability (Massachusetts) OR Employers Liability (New York), then print the following static text below 'Defense' static text:
 "In any jurisdiction, state, or province where the amount of Employers Liability Insurance provided by the Underlying Insurer(s) is by law "Unlimited", the underlying Employers' Liability Limit(s) shown in the above schedule do not apply and no coverage shall be provided for Employers Liability under this policy."</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>8114</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(A) Automobile Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Auto Liability is added more than once on UI, then print the details of Auto Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Auto Liability is added more than once on UI, then print the details of Auto Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>8117</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (A) Automobile Liability
+Bodily Injury and Property Damage Combined Single Limit $ _ Each Accident</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print this limit value of Auto Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Combined Single Limit</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.combSingleLim
+)</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print this limit value of Auto Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>8118</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (A) Automobile Liability</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the Insurer details of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the Insurer details of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>8119</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (A) Automobile Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the effective date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the effective date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>8120</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (A) Automobile Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the expiration date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the expiration date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>8121</v>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>(A) Automobile Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the defense cost value of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N53" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the defense cost value of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>8122</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(B) Commercial General Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If General Liability is added more than once on UI, then print the details of General Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If General Liability is added more than once on UI, then print the details of General Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>8123</v>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+$ Each Occurrence Limit</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Each Occurrence</t>
+        </is>
+      </c>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.eachOcc
+)</t>
+        </is>
+      </c>
+      <c r="O55" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>8124</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Products/Completed Operations Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Products-Completed Operations Aggregate</t>
+        </is>
+      </c>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.proComOpAgg
+)</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>8125</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+General Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;General Aggregate</t>
+        </is>
+      </c>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.generalAgg
+)</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>8126</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Policy Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Policy Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.aggLimAppl
+)</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>8127</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Personal and Advertising Injury Limit</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Personal and Advertising Injury Limit</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.perAdvInjLim
+)</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>8128</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (B) Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the Insurer details of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the Insurer details of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>8129</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (B) Commercial General Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the effective date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the effective date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>8130</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (B) Commercial General Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the expiration date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the expiration date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>8131</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>(B) Commercial General Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the defense cost value of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the defense cost value of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>8132</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(C) Employers Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is/are added more than once on UI, then print the details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is/are added more than once on UI, then print the details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>8133</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Accident $ Each Accident</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Accident - Each Accident</t>
+        </is>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByAccEachAcci
+)</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>8134</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Disease $ Policy Limit</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Disease - Policy Limit</t>
+        </is>
+      </c>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByDisPolicyLim
+)</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>8135</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Disease $ Each Employee</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Disease - Each Employee</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByDisEachEmpli
+)</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>8136</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (C) Employers Liability</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the Insurer details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the Insurer details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>8137</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (C) Employers Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the effective date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the effective date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>8138</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (C) Employers Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the expiration date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the expiration date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>8139</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>(C) Employers Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the defense cost value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the defense cost value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>8140</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(D) Employee Benefits
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employee Benefits Liability is added more than once on UI, then print the details of Employee Benefits Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employee Benefits Liability is added more than once on UI, then print the details of Employee Benefits Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>8141</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+$ Each Employee</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Each Employee</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.eachEmp
+)</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>8142</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+Aggregate</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Aggregate</t>
+        </is>
+      </c>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulAggregate
+)</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>8143</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+Retroactive Date</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print retroactive date of Employee Benefits Liability underlying polcy(ies) on the form
+•Print this below Aggregate field on form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)
+For ex: October 21 2026 Retroactive Date</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Retroactive Date</t>
+        </is>
+      </c>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then {
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.mmecRetroDate
+} else [
+  Do NOT print retroactive date on the form
+]</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print retroactive date of Employee Benefits Liability underlying polcy(ies) on the form
+•Print this below Aggregate field on form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)
+For ex: October 21 2026 Retroactive Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>8144</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (D) Employee Benefits</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the Insurer details of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M76" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the Insurer details of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>8145</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (D) Employee Benefits
+From:</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the effective date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the effective date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>8146</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (D) Employee Benefits
+To:</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the expiration date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the expiration date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>8147</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>(D) Employee Benefits
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the defense cost value of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the defense cost value of Employee Benefits Liability underlying polcy(ies) on the form</t>
         </is>
       </c>
     </row>
@@ -8382,4 +11167,2877 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="68" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Guidewire PolicyCenter to SmartCOMM XPath Mapping - CUU 003 0805</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Excel Row #</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>LOB</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Form Type</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Content Type</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Form Number</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Form Name</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Form Field Name in Form</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate (Y/N)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>GW Screen Info</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Conditions if any</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Field Type</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>GW Field Name</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>XPATH (SMARTCOMM payload)</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Conditions (if any) SMARTCOMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>8114</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(A) Automobile Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Auto Liability is added more than once on UI, then print the details of Auto Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Auto Liability is added more than once on UI, then print the details of Auto Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>8117</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (A) Automobile Liability
+Bodily Injury and Property Damage Combined Single Limit $ _ Each Accident</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print this limit value of Auto Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Combined Single Limit</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.combSingleLim
+)</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print this limit value of Auto Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>8118</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (A) Automobile Liability</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the Insurer details of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the Insurer details of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>8119</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (A) Automobile Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the effective date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the effective date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>8120</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (A) Automobile Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the expiration date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the expiration date of Auto Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>8121</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>(A) Automobile Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the defense cost value of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Auto Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Auto Liability on 'Underlying' screen, then map/print the defense cost value of Auto Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>8122</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(B) Commercial General Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If General Liability is added more than once on UI, then print the details of General Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If General Liability is added more than once on UI, then print the details of General Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8123</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+$ Each Occurrence Limit</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Each Occurrence</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.eachOcc
+)</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>8124</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Products/Completed Operations Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Products-Completed Operations Aggregate</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.proComOpAgg
+)</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>8125</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+General Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;General Aggregate</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.generalAgg
+)</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>8126</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Policy Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Policy Aggregate Limit</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.aggLimAppl
+)</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>8127</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (B) Commercial General Liability
+Personal and Advertising Injury Limit</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Personal and Advertising Injury Limit</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.perAdvInjLim
+)</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print this limit value of General Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>8128</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (B) Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the Insurer details of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the Insurer details of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>8129</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (B) Commercial General Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the effective date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the effective date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>8130</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (B) Commercial General Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the expiration date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the expiration date of General Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>8131</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>(B) Commercial General Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the defense cost value of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == General Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = General Liability on 'Underlying' screen, then map/print the defense cost value of General Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>8132</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(C) Employers Liability
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is/are added more than once on UI, then print the details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) is/are added more than once on UI, then print the details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>8133</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Accident $ Each Accident</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Accident - Each Accident</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByAccEachAcci
+)</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>8134</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Disease $ Policy Limit</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Disease - Policy Limit</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByDisPolicyLim
+)</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>8135</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (C) Employers Liability
+Bodily Injury by Disease $ Each Employee</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Bodily Injury by Disease - Each Employee</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.bodilyInjuryByDisEachEmpli
+)</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print this limit value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>8136</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (C) Employers Liability</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the Insurer details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the Insurer details of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>8137</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (C) Employers Liability
+From:</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the effective date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the effective date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>8138</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (C) Employers Liability
+To:</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the expiration date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the expiration date of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>8139</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>(C) Employers Liability
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the defense cost value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (All States) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (Massachusetts) OR
+ pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employers Liability (New York))
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) on 'Underlying' screen, then map/print the defense cost value of Employers Liability (All States)/Employers Liability (Massachusetts)/Employers Liability (New York) underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>8140</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Type of Policy
+(D) Employee Benefits
+Note to INT/SC team regarding printing this row on form</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employee Benefits Liability is added more than once on UI, then print the details of Employee Benefits Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name
+)</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability is added on 'Underlying' screen, then print this row on form, otherwise do NOT print
+•If Employee Benefits Liability is added more than once on UI, then print the details of Employee Benefits Liability underlying policies one below the other on form</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>8141</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+$ Each Employee</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Each Employee</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.eachEmp
+)</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>8142</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+Aggregate</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Monetary Amnt</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Aggregate</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulAggregate
+)</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print this limit and its value of Employee Benefits Liability underlying polcy(ies) on the form
+•Do NOT print the limit values in decimals</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>8143</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Applicable Limits - (D) Employee Benefits
+Retroactive Date</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print retroactive date of Employee Benefits Liability underlying polcy(ies) on the form
+•Print this below Aggregate field on form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)
+For ex: October 21 2026 Retroactive Date</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Retroactive Date</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ctrlULPol == Yes)
+AND (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then {
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.mmecRetroDate
+} else [
+  Do NOT print retroactive date on the form
+]</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print retroactive date of Employee Benefits Liability underlying polcy(ies) on the form
+•Print this below Aggregate field on form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)
+For ex: October 21 2026 Retroactive Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>8144</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Insurer - (D) Employee Benefits</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the Insurer details of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Text</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Underlying Carrier</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCarrier
+)</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the Insurer details of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>8145</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (D) Employee Benefits
+From:</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the effective date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Effective Date</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulEffDate
+)</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the effective date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>8146</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Policy Period - (D) Employee Benefits
+To:</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the expiration date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down
+Month DD, YYYY</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Expiration Date</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulExpDate
+)</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the expiration date of Employee Benefits Liability underlying polcy(ies) on the form
+•Date value should be formatted to Month DD, YYYY (refer Field type column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>8147</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>MVP (DF 4 DL 26Q4 SP1)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>MM EC</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Dynamic</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>CUU 003 0805</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Schedule Of Underlying Insurance</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>(D) Employee Benefits
+Defense Cost</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>'MM Commercial Excess and Umbrella' screen -&gt; 'Details and Coverages' tab -&gt; Coverage Details
+Underlying screen</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the defense cost value of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Drop Down</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>&gt;Type of Coverage
+&gt;Coverage Type
+&gt;Defense Cost</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>If (pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.typeOfCoverage.name == Lead Umbrella) and
+(pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.ulCovType.name == Employee Benefits Liability)
+Then (
+  pcDocumentCreationRequest.policyPeriod.lines.CommXSUmbLine.underlyings.underlyings.defenseCost.name
+)</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>•If 'Type of Coverage' = Lead Umbrella on 'MM Commercial Excess and Umbrella' screen AND Coverage Type = Employee Benefits Liability on 'Underlying' screen, then map/print the defense cost value of Employee Benefits Liability underlying polcy(ies) on the form</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>